--- a/tame_output/ON/bt/strategyON_20231231.xlsx
+++ b/tame_output/ON/bt/strategyON_20231231.xlsx
@@ -977,7 +977,7 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>20.0%</t>
+          <t>19.9%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
@@ -43560,10 +43560,10 @@
         <v>3.125771717521518</v>
       </c>
       <c r="D1828" t="n">
-        <v>0.0622006308015825</v>
+        <v>0.06209380951309612</v>
       </c>
       <c r="E1828" t="n">
-        <v>3.150295545528404</v>
+        <v>3.150252817013009</v>
       </c>
       <c r="F1828" t="n">
         <v>1.693598838607934</v>

--- a/tame_output/ON/bt/strategyON_20231231.xlsx
+++ b/tame_output/ON/bt/strategyON_20231231.xlsx
@@ -595,7 +595,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>49.9%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -736,7 +736,7 @@
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>92.7%</t>
+          <t>92.2%</t>
         </is>
       </c>
     </row>
@@ -901,12 +901,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-27.8%</t>
+          <t>-28.0%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>77.3%</t>
+          <t>77.5%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -934,12 +934,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>86.0%</t>
+          <t>86.1%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>68.4%</t>
+          <t>68.8%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -977,12 +977,12 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>19.9%</t>
+          <t>20.2%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-27.7%</t>
+          <t>-28.0%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -997,7 +997,7 @@
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>63.3%</t>
+          <t>63.5%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1012,12 +1012,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>480.9%</t>
+          <t>480.3%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-160.4%</t>
+          <t>-159.9%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1042,7 +1042,7 @@
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>-136.2%</t>
+          <t>-136.4%</t>
         </is>
       </c>
     </row>
@@ -1059,7 +1059,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>41.8%</t>
+          <t>41.9%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1092,12 +1092,12 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>38.4%</t>
+          <t>38.5%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>90.8%</t>
+          <t>91.1%</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
@@ -1107,11 +1107,11 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>2023-11-26</t>
+          <t>2023-12-01</t>
         </is>
       </c>
       <c r="N5" t="n">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="O5" t="inlineStr">
         <is>
@@ -1130,12 +1130,12 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>12.1%</t>
+          <t>12.2%</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>-19.5%</t>
+          <t>-19.8%</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
@@ -1145,12 +1145,12 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>68.0%</t>
+          <t>68.1%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>34.9%</t>
+          <t>35.0%</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
@@ -1165,12 +1165,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-19.2%</t>
+          <t>-19.4%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>40.1%</t>
+          <t>40.0%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1195,7 +1195,7 @@
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>-27.4%</t>
+          <t>-27.5%</t>
         </is>
       </c>
     </row>
@@ -1207,22 +1207,22 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>23.5%</t>
+          <t>21.4%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>48.8%</t>
+          <t>48.9%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>0.48</t>
+          <t>0.44</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>54.6%</t>
+          <t>54.5%</t>
         </is>
       </c>
       <c r="F6" t="n">
@@ -1240,7 +1240,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>42.8%</t>
+          <t>43.0%</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1250,7 +1250,7 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>94.1%</t>
+          <t>94.6%</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
@@ -1288,7 +1288,7 @@
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>-18.7%</t>
+          <t>-19.3%</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
@@ -1298,17 +1298,17 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>35.7%</t>
+          <t>33.4%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>40.0%</t>
+          <t>40.1%</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>0.9</t>
+          <t>0.8</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -1318,12 +1318,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>12.2%</t>
+          <t>11.2%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>184.0%</t>
+          <t>191.6%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1348,7 +1348,7 @@
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>-39.9%</t>
+          <t>-47.9%</t>
         </is>
       </c>
     </row>
@@ -1360,7 +1360,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>110.1%</t>
+          <t>108.1%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1370,7 +1370,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2.71</t>
+          <t>2.65</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1403,7 +1403,7 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>78.2%</t>
+          <t>79.2%</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -1413,11 +1413,11 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>2023-11-26</t>
+          <t>2023-11-30</t>
         </is>
       </c>
       <c r="N7" t="n">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="O7" t="inlineStr">
         <is>
@@ -1441,7 +1441,7 @@
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>-14.0%</t>
+          <t>-14.5%</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
@@ -1451,7 +1451,7 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>104.9%</t>
+          <t>102.9%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
@@ -1461,7 +1461,7 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>3.1</t>
+          <t>3.0</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -1476,7 +1476,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>37.0%</t>
+          <t>36.9%</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>3.1%</t>
+          <t>-1.7%</t>
         </is>
       </c>
     </row>
@@ -42801,16 +42801,16 @@
         <v>3.082620445523309</v>
       </c>
       <c r="D1795" t="n">
-        <v>-4.200334620068173</v>
+        <v>-4.280178369679041</v>
       </c>
       <c r="E1795" t="n">
-        <v>1.402130173182293</v>
+        <v>1.370192673337946</v>
       </c>
       <c r="F1795" t="n">
-        <v>-0.2966495456029348</v>
+        <v>-0.376493295213803</v>
       </c>
       <c r="G1795" t="n">
-        <v>2.90463071816155</v>
+        <v>2.856724468395029</v>
       </c>
     </row>
     <row r="1796">
@@ -42824,16 +42824,16 @@
         <v>3.079594415968698</v>
       </c>
       <c r="D1796" t="n">
-        <v>-4.20218002964504</v>
+        <v>-4.282023779255908</v>
       </c>
       <c r="E1796" t="n">
-        <v>1.398365979796935</v>
+        <v>1.366428479952588</v>
       </c>
       <c r="F1796" t="n">
-        <v>-0.2966495456029348</v>
+        <v>-0.376493295213803</v>
       </c>
       <c r="G1796" t="n">
-        <v>2.901604688606939</v>
+        <v>2.853698438840418</v>
       </c>
     </row>
     <row r="1797">
@@ -42847,16 +42847,16 @@
         <v>3.079532703829831</v>
       </c>
       <c r="D1797" t="n">
-        <v>-4.200681597119941</v>
+        <v>-4.280525346730809</v>
       </c>
       <c r="E1797" t="n">
-        <v>1.398903640668108</v>
+        <v>1.366966140823761</v>
       </c>
       <c r="F1797" t="n">
-        <v>-0.2951511130778359</v>
+        <v>-0.3749948626887041</v>
       </c>
       <c r="G1797" t="n">
-        <v>2.902442035983131</v>
+        <v>2.85453578621661</v>
       </c>
     </row>
     <row r="1798">
@@ -42870,16 +42870,16 @@
         <v>3.080810681773143</v>
       </c>
       <c r="D1798" t="n">
-        <v>-4.208745849312675</v>
+        <v>-4.288589598923543</v>
       </c>
       <c r="E1798" t="n">
-        <v>1.396955917734326</v>
+        <v>1.365018417889979</v>
       </c>
       <c r="F1798" t="n">
-        <v>-0.3032153652705697</v>
+        <v>-0.3830591148814379</v>
       </c>
       <c r="G1798" t="n">
-        <v>2.898881462610803</v>
+        <v>2.850975212844282</v>
       </c>
     </row>
     <row r="1799">
@@ -42893,16 +42893,16 @@
         <v>3.080810681773143</v>
       </c>
       <c r="D1799" t="n">
-        <v>-4.210075816773887</v>
+        <v>-4.289919566384755</v>
       </c>
       <c r="E1799" t="n">
-        <v>1.396423930749841</v>
+        <v>1.364486430905494</v>
       </c>
       <c r="F1799" t="n">
-        <v>-0.3032153652705697</v>
+        <v>-0.3830591148814379</v>
       </c>
       <c r="G1799" t="n">
-        <v>2.898881462610803</v>
+        <v>2.850975212844282</v>
       </c>
     </row>
     <row r="1800">
@@ -42916,16 +42916,16 @@
         <v>3.083027154880305</v>
       </c>
       <c r="D1800" t="n">
-        <v>-3.982211134040377</v>
+        <v>-4.062054883651244</v>
       </c>
       <c r="E1800" t="n">
-        <v>1.489786276950408</v>
+        <v>1.45784877710606</v>
       </c>
       <c r="F1800" t="n">
-        <v>-0.3032153652705697</v>
+        <v>-0.3830591148814379</v>
       </c>
       <c r="G1800" t="n">
-        <v>2.901097935717965</v>
+        <v>2.853191685951444</v>
       </c>
     </row>
     <row r="1801">
@@ -42939,16 +42939,16 @@
         <v>3.090561751225397</v>
       </c>
       <c r="D1801" t="n">
-        <v>-3.734109570173159</v>
+        <v>-3.813953319784027</v>
       </c>
       <c r="E1801" t="n">
-        <v>1.596561498842386</v>
+        <v>1.564623998998039</v>
       </c>
       <c r="F1801" t="n">
-        <v>-0.3032153652705697</v>
+        <v>-0.3830591148814379</v>
       </c>
       <c r="G1801" t="n">
-        <v>2.908632532063057</v>
+        <v>2.860726282296536</v>
       </c>
     </row>
     <row r="1802">
@@ -42962,16 +42962,16 @@
         <v>3.091984762198855</v>
       </c>
       <c r="D1802" t="n">
-        <v>-3.437271170779829</v>
+        <v>-3.517114920390697</v>
       </c>
       <c r="E1802" t="n">
-        <v>1.716719869573176</v>
+        <v>1.684782369728829</v>
       </c>
       <c r="F1802" t="n">
-        <v>-0.1883608767894421</v>
+        <v>-0.2682046264003102</v>
       </c>
       <c r="G1802" t="n">
-        <v>2.978968236125191</v>
+        <v>2.93106198635867</v>
       </c>
     </row>
     <row r="1803">
@@ -42985,16 +42985,16 @@
         <v>3.093661836664541</v>
       </c>
       <c r="D1803" t="n">
-        <v>-3.133631613954393</v>
+        <v>-3.213475363565261</v>
       </c>
       <c r="E1803" t="n">
-        <v>1.839852766769037</v>
+        <v>1.80791526692469</v>
       </c>
       <c r="F1803" t="n">
-        <v>-0.1883608767894421</v>
+        <v>-0.2682046264003102</v>
       </c>
       <c r="G1803" t="n">
-        <v>2.980645310590877</v>
+        <v>2.932739060824357</v>
       </c>
     </row>
     <row r="1804">
@@ -43008,16 +43008,16 @@
         <v>3.089601258113999</v>
       </c>
       <c r="D1804" t="n">
-        <v>-2.844611007513684</v>
+        <v>-2.924454757124552</v>
       </c>
       <c r="E1804" t="n">
-        <v>1.951400430794778</v>
+        <v>1.919462930950431</v>
       </c>
       <c r="F1804" t="n">
-        <v>-0.1883608767894421</v>
+        <v>-0.2682046264003102</v>
       </c>
       <c r="G1804" t="n">
-        <v>2.976584732040335</v>
+        <v>2.928678482273814</v>
       </c>
     </row>
     <row r="1805">
@@ -43031,16 +43031,16 @@
         <v>3.094821397458016</v>
       </c>
       <c r="D1805" t="n">
-        <v>-2.559891080249787</v>
+        <v>-2.639734829860655</v>
       </c>
       <c r="E1805" t="n">
-        <v>2.070508541044355</v>
+        <v>2.038571041200008</v>
       </c>
       <c r="F1805" t="n">
-        <v>0.09635905047445509</v>
+        <v>0.01651530086358693</v>
       </c>
       <c r="G1805" t="n">
-        <v>3.152636827742691</v>
+        <v>3.10473057797617</v>
       </c>
     </row>
     <row r="1806">
@@ -43054,16 +43054,16 @@
         <v>3.100133560631823</v>
       </c>
       <c r="D1806" t="n">
-        <v>-2.276129410758247</v>
+        <v>-2.355973160369115</v>
       </c>
       <c r="E1806" t="n">
-        <v>2.189325372014778</v>
+        <v>2.15738787217043</v>
       </c>
       <c r="F1806" t="n">
-        <v>0.09635905047445509</v>
+        <v>0.01651530086358693</v>
       </c>
       <c r="G1806" t="n">
-        <v>3.157948990916498</v>
+        <v>3.110042741149977</v>
       </c>
     </row>
     <row r="1807">
@@ -43077,16 +43077,16 @@
         <v>3.093376148078457</v>
       </c>
       <c r="D1807" t="n">
-        <v>-2.014481016365607</v>
+        <v>-2.094324765976475</v>
       </c>
       <c r="E1807" t="n">
-        <v>2.287227317218467</v>
+        <v>2.25528981737412</v>
       </c>
       <c r="F1807" t="n">
-        <v>0.3580074448670957</v>
+        <v>0.2781636952562276</v>
       </c>
       <c r="G1807" t="n">
-        <v>3.308180614998716</v>
+        <v>3.260274365232195</v>
       </c>
     </row>
     <row r="1808">
@@ -43100,16 +43100,16 @@
         <v>3.090839823094569</v>
       </c>
       <c r="D1808" t="n">
-        <v>-1.700314578226274</v>
+        <v>-1.780158327837142</v>
       </c>
       <c r="E1808" t="n">
-        <v>2.410357567490313</v>
+        <v>2.378420067645966</v>
       </c>
       <c r="F1808" t="n">
-        <v>0.6721738830064281</v>
+        <v>0.59233013339556</v>
       </c>
       <c r="G1808" t="n">
-        <v>3.494144152898428</v>
+        <v>3.446237903131907</v>
       </c>
     </row>
     <row r="1809">
@@ -43123,16 +43123,16 @@
         <v>3.109254206721308</v>
       </c>
       <c r="D1809" t="n">
-        <v>-1.577802874120502</v>
+        <v>-1.65764662373137</v>
       </c>
       <c r="E1809" t="n">
-        <v>2.477776632759361</v>
+        <v>2.445839132915014</v>
       </c>
       <c r="F1809" t="n">
-        <v>0.7946855871122005</v>
+        <v>0.7148418375013323</v>
       </c>
       <c r="G1809" t="n">
-        <v>3.586065558988631</v>
+        <v>3.53815930922211</v>
       </c>
     </row>
     <row r="1810">
@@ -43146,16 +43146,16 @@
         <v>3.119070330776787</v>
       </c>
       <c r="D1810" t="n">
-        <v>-1.416414340193773</v>
+        <v>-1.496258089804641</v>
       </c>
       <c r="E1810" t="n">
-        <v>2.552148170385531</v>
+        <v>2.520210670541184</v>
       </c>
       <c r="F1810" t="n">
-        <v>0.9560741210389289</v>
+        <v>0.8762303714280607</v>
       </c>
       <c r="G1810" t="n">
-        <v>3.692714803400146</v>
+        <v>3.644808553633625</v>
       </c>
     </row>
     <row r="1811">
@@ -43169,16 +43169,16 @@
         <v>3.132597942828719</v>
       </c>
       <c r="D1811" t="n">
-        <v>-1.236668149045267</v>
+        <v>-1.316511898656135</v>
       </c>
       <c r="E1811" t="n">
-        <v>2.637574258896865</v>
+        <v>2.605636759052518</v>
       </c>
       <c r="F1811" t="n">
-        <v>0.9560741210389289</v>
+        <v>0.8762303714280607</v>
       </c>
       <c r="G1811" t="n">
-        <v>3.706242415452078</v>
+        <v>3.658336165685557</v>
       </c>
     </row>
     <row r="1812">
@@ -43192,16 +43192,16 @@
         <v>3.139185323079984</v>
       </c>
       <c r="D1812" t="n">
-        <v>-1.077867222574044</v>
+        <v>-1.157710972184912</v>
       </c>
       <c r="E1812" t="n">
-        <v>2.70768200973662</v>
+        <v>2.675744509892273</v>
       </c>
       <c r="F1812" t="n">
-        <v>0.9560741210389289</v>
+        <v>0.8762303714280607</v>
       </c>
       <c r="G1812" t="n">
-        <v>3.712829795703343</v>
+        <v>3.664923545936823</v>
       </c>
     </row>
     <row r="1813">
@@ -43215,16 +43215,16 @@
         <v>3.128096071514691</v>
       </c>
       <c r="D1813" t="n">
-        <v>-0.9850787642686674</v>
+        <v>-1.064922513879535</v>
       </c>
       <c r="E1813" t="n">
-        <v>2.733708141493477</v>
+        <v>2.70177064164913</v>
       </c>
       <c r="F1813" t="n">
-        <v>1.048862579344306</v>
+        <v>0.9690188297334376</v>
       </c>
       <c r="G1813" t="n">
-        <v>3.757413619121276</v>
+        <v>3.709507369354755</v>
       </c>
     </row>
     <row r="1814">
@@ -43238,16 +43238,16 @@
         <v>3.123696569025415</v>
       </c>
       <c r="D1814" t="n">
-        <v>-0.8910582688978255</v>
+        <v>-0.9709020185086934</v>
       </c>
       <c r="E1814" t="n">
-        <v>2.766916837152538</v>
+        <v>2.734979337308191</v>
       </c>
       <c r="F1814" t="n">
-        <v>1.058705019837289</v>
+        <v>0.9788612702264211</v>
       </c>
       <c r="G1814" t="n">
-        <v>3.75891958092779</v>
+        <v>3.711013331161269</v>
       </c>
     </row>
     <row r="1815">
@@ -43261,16 +43261,16 @@
         <v>3.109676345532145</v>
       </c>
       <c r="D1815" t="n">
-        <v>-0.8009553009913024</v>
+        <v>-0.8807990506021703</v>
       </c>
       <c r="E1815" t="n">
-        <v>2.788937800821877</v>
+        <v>2.75700030097753</v>
       </c>
       <c r="F1815" t="n">
-        <v>1.061763214125075</v>
+        <v>0.9819194645142068</v>
       </c>
       <c r="G1815" t="n">
-        <v>3.746734274007192</v>
+        <v>3.698828024240671</v>
       </c>
     </row>
     <row r="1816">
@@ -43284,16 +43284,16 @@
         <v>3.127125924287274</v>
       </c>
       <c r="D1816" t="n">
-        <v>-0.7568261302697272</v>
+        <v>-0.8366698798805952</v>
       </c>
       <c r="E1816" t="n">
-        <v>2.824039047865636</v>
+        <v>2.792101548021289</v>
       </c>
       <c r="F1816" t="n">
-        <v>1.145782387112345</v>
+        <v>1.065938637501477</v>
       </c>
       <c r="G1816" t="n">
-        <v>3.814595356554682</v>
+        <v>3.766689106788162</v>
       </c>
     </row>
     <row r="1817">
@@ -43307,16 +43307,16 @@
         <v>3.126153974671351</v>
       </c>
       <c r="D1817" t="n">
-        <v>-0.7470560860920324</v>
+        <v>-0.8268998357029004</v>
       </c>
       <c r="E1817" t="n">
-        <v>2.826975115920791</v>
+        <v>2.795037616076444</v>
       </c>
       <c r="F1817" t="n">
-        <v>1.225141278167411</v>
+        <v>1.145297528556543</v>
       </c>
       <c r="G1817" t="n">
-        <v>3.861238741571799</v>
+        <v>3.813332491805278</v>
       </c>
     </row>
     <row r="1818">
@@ -43330,16 +43330,16 @@
         <v>3.115456695754193</v>
       </c>
       <c r="D1818" t="n">
-        <v>-0.7104177633240578</v>
+        <v>-0.7902615129349257</v>
       </c>
       <c r="E1818" t="n">
-        <v>2.830933166110824</v>
+        <v>2.798995666266476</v>
       </c>
       <c r="F1818" t="n">
-        <v>1.225141278167411</v>
+        <v>1.145297528556543</v>
       </c>
       <c r="G1818" t="n">
-        <v>3.850541462654641</v>
+        <v>3.802635212888121</v>
       </c>
     </row>
     <row r="1819">
@@ -43353,16 +43353,16 @@
         <v>3.125373651216407</v>
       </c>
       <c r="D1819" t="n">
-        <v>-0.6617720848543245</v>
+        <v>-0.7416158344651924</v>
       </c>
       <c r="E1819" t="n">
-        <v>2.860308392960931</v>
+        <v>2.828370893116583</v>
       </c>
       <c r="F1819" t="n">
-        <v>1.273786956637144</v>
+        <v>1.193943207026277</v>
       </c>
       <c r="G1819" t="n">
-        <v>3.889645825198695</v>
+        <v>3.841739575432175</v>
       </c>
     </row>
     <row r="1820">
@@ -43376,16 +43376,16 @@
         <v>3.132226628875955</v>
       </c>
       <c r="D1820" t="n">
-        <v>-0.6012921824349222</v>
+        <v>-0.6811359320457901</v>
       </c>
       <c r="E1820" t="n">
-        <v>2.891353331588239</v>
+        <v>2.859415831743892</v>
       </c>
       <c r="F1820" t="n">
-        <v>1.334266859056547</v>
+        <v>1.254423109445679</v>
       </c>
       <c r="G1820" t="n">
-        <v>3.932786744309884</v>
+        <v>3.884880494543363</v>
       </c>
     </row>
     <row r="1821">
@@ -43399,16 +43399,16 @@
         <v>3.134450814492048</v>
       </c>
       <c r="D1821" t="n">
-        <v>-0.5187421149188052</v>
+        <v>-0.5985858645296731</v>
       </c>
       <c r="E1821" t="n">
-        <v>2.926597544210779</v>
+        <v>2.894660044366432</v>
       </c>
       <c r="F1821" t="n">
-        <v>1.334266859056547</v>
+        <v>1.254423109445679</v>
       </c>
       <c r="G1821" t="n">
-        <v>3.935010929925977</v>
+        <v>3.887104680159457</v>
       </c>
     </row>
     <row r="1822">
@@ -43422,16 +43422,16 @@
         <v>3.121045839271831</v>
       </c>
       <c r="D1822" t="n">
-        <v>-0.4409060272235886</v>
+        <v>-0.5207497768344564</v>
       </c>
       <c r="E1822" t="n">
-        <v>2.944327004068649</v>
+        <v>2.912389504224302</v>
       </c>
       <c r="F1822" t="n">
-        <v>1.412848811712671</v>
+        <v>1.333005062101803</v>
       </c>
       <c r="G1822" t="n">
-        <v>3.968755126299436</v>
+        <v>3.920848876532915</v>
       </c>
     </row>
     <row r="1823">
@@ -43445,16 +43445,16 @@
         <v>3.126711518797542</v>
       </c>
       <c r="D1823" t="n">
-        <v>-0.3240293616086833</v>
+        <v>-0.4038731112195512</v>
       </c>
       <c r="E1823" t="n">
-        <v>2.996743349840322</v>
+        <v>2.964805849995975</v>
       </c>
       <c r="F1823" t="n">
-        <v>1.495418153172296</v>
+        <v>1.415574403561428</v>
       </c>
       <c r="G1823" t="n">
-        <v>4.023962410700921</v>
+        <v>3.976056160934401</v>
       </c>
     </row>
     <row r="1824">
@@ -43468,16 +43468,16 @@
         <v>3.130543841755795</v>
       </c>
       <c r="D1824" t="n">
-        <v>-0.2594743932519631</v>
+        <v>-0.339318142862831</v>
       </c>
       <c r="E1824" t="n">
-        <v>3.026397660141263</v>
+        <v>2.994460160296916</v>
       </c>
       <c r="F1824" t="n">
-        <v>1.559973121529016</v>
+        <v>1.480129371918149</v>
       </c>
       <c r="G1824" t="n">
-        <v>4.066527714673207</v>
+        <v>4.018621464906686</v>
       </c>
     </row>
     <row r="1825">
@@ -43491,16 +43491,16 @@
         <v>3.133773427784875</v>
       </c>
       <c r="D1825" t="n">
-        <v>-0.1333660405243163</v>
+        <v>-0.2132097901351842</v>
       </c>
       <c r="E1825" t="n">
-        <v>3.080070587261402</v>
+        <v>3.048133087417055</v>
       </c>
       <c r="F1825" t="n">
-        <v>1.559973121529016</v>
+        <v>1.480129371918149</v>
       </c>
       <c r="G1825" t="n">
-        <v>4.069757300702286</v>
+        <v>4.021851050935766</v>
       </c>
     </row>
     <row r="1826">
@@ -43514,16 +43514,16 @@
         <v>3.1338083988329</v>
       </c>
       <c r="D1826" t="n">
-        <v>-0.05721098262461272</v>
+        <v>-0.1370547322354806</v>
       </c>
       <c r="E1826" t="n">
-        <v>3.110567581469308</v>
+        <v>3.078630081624961</v>
       </c>
       <c r="F1826" t="n">
-        <v>1.63612817942872</v>
+        <v>1.556284429817852</v>
       </c>
       <c r="G1826" t="n">
-        <v>4.115485306490134</v>
+        <v>4.067579056723614</v>
       </c>
     </row>
     <row r="1827">
@@ -43537,16 +43537,16 @@
         <v>3.129380481089744</v>
       </c>
       <c r="D1827" t="n">
-        <v>0.0002596765546009627</v>
+        <v>-0.07958407305626691</v>
       </c>
       <c r="E1827" t="n">
-        <v>3.129127927397838</v>
+        <v>3.097190427553491</v>
       </c>
       <c r="F1827" t="n">
-        <v>1.693598838607934</v>
+        <v>1.613755088997066</v>
       </c>
       <c r="G1827" t="n">
-        <v>4.145539784254506</v>
+        <v>4.097633534487986</v>
       </c>
     </row>
     <row r="1828">
@@ -43554,22 +43554,22 @@
         <v>45290</v>
       </c>
       <c r="B1828" t="n">
-        <v>3.16284714667758</v>
+        <v>3.157971701303786</v>
       </c>
       <c r="C1828" t="n">
         <v>3.125771717521518</v>
       </c>
       <c r="D1828" t="n">
-        <v>0.06209380951309612</v>
+        <v>0.06053743492622976</v>
       </c>
       <c r="E1828" t="n">
-        <v>3.150252817013009</v>
+        <v>3.149630267178263</v>
       </c>
       <c r="F1828" t="n">
-        <v>1.693598838607934</v>
+        <v>1.613755088997066</v>
       </c>
       <c r="G1828" t="n">
-        <v>4.14193102068628</v>
+        <v>4.094024770919758</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20231231.xlsx
+++ b/tame_output/ON/bt/strategyON_20231231.xlsx
@@ -901,17 +901,17 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-28.0%</t>
+          <t>-29.0%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>77.5%</t>
+          <t>77.3%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>-0.36</t>
+          <t>-0.37</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -939,7 +939,7 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>68.8%</t>
+          <t>68.4%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -977,7 +977,7 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>20.2%</t>
+          <t>20.0%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
@@ -992,17 +992,17 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-15.4%</t>
+          <t>-16.7%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>63.5%</t>
+          <t>63.4%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>-0.2</t>
+          <t>-0.3</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -1012,7 +1012,7 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>480.3%</t>
+          <t>478.7%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
@@ -1042,7 +1042,7 @@
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>-136.4%</t>
+          <t>-143.9%</t>
         </is>
       </c>
     </row>
@@ -1054,17 +1054,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>71.5%</t>
+          <t>70.5%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>41.9%</t>
+          <t>41.8%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>1.71</t>
+          <t>1.68</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1092,7 +1092,7 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>38.5%</t>
+          <t>38.4%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -1130,7 +1130,7 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>12.2%</t>
+          <t>12.1%</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -1145,12 +1145,12 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>68.1%</t>
+          <t>67.0%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>35.0%</t>
+          <t>34.9%</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
@@ -1165,7 +1165,7 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-19.4%</t>
+          <t>-19.3%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
@@ -1195,7 +1195,7 @@
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>-27.5%</t>
+          <t>-30.5%</t>
         </is>
       </c>
     </row>
@@ -43560,10 +43560,10 @@
         <v>3.125771717521518</v>
       </c>
       <c r="D1828" t="n">
-        <v>0.06053743492622976</v>
+        <v>-0.01476176004609508</v>
       </c>
       <c r="E1828" t="n">
-        <v>3.149630267178263</v>
+        <v>3.119510589189333</v>
       </c>
       <c r="F1828" t="n">
         <v>1.613755088997066</v>
